--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="123">
   <si>
     <t>原始SKU</t>
   </si>
@@ -347,6 +347,18 @@
   </si>
   <si>
     <t>008-137-12-1</t>
+  </si>
+  <si>
+    <t>006-137-12G</t>
+  </si>
+  <si>
+    <t>005-152-12</t>
+  </si>
+  <si>
+    <t>005-152-12G</t>
+  </si>
+  <si>
+    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS007-30-TWIN</t>
@@ -702,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -718,7 +730,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -726,7 +738,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -734,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -742,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -750,7 +762,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -758,7 +770,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -766,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -774,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -782,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -790,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -798,7 +810,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -806,7 +818,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -814,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -822,7 +834,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -830,7 +842,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -838,7 +850,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -846,7 +858,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -854,7 +866,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -862,7 +874,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -870,7 +882,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -878,7 +890,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -886,7 +898,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -894,7 +906,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -902,7 +914,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -910,7 +922,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -918,7 +930,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -926,7 +938,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -934,7 +946,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -942,7 +954,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -950,7 +962,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -958,7 +970,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -966,7 +978,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1582,6 +1594,38 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
         <v>35</v>
       </c>
     </row>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="119">
   <si>
     <t>原始SKU</t>
   </si>
@@ -346,19 +346,7 @@
     <t>009-192-14B</t>
   </si>
   <si>
-    <t>008-137-12-1</t>
-  </si>
-  <si>
     <t>006-137-12G</t>
-  </si>
-  <si>
-    <t>005-152-12</t>
-  </si>
-  <si>
-    <t>005-152-12G</t>
-  </si>
-  <si>
-    <t>WS008-137-12C</t>
   </si>
   <si>
     <t>WS007-30-TWIN</t>
@@ -714,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -730,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -738,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -746,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -754,7 +742,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -762,7 +750,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -770,7 +758,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -778,7 +766,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -786,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -794,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -802,7 +790,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -810,7 +798,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -818,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -826,7 +814,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -834,7 +822,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -842,7 +830,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -850,7 +838,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -858,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -866,7 +854,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -874,7 +862,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -882,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -890,7 +878,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -898,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -906,7 +894,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -914,7 +902,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -922,7 +910,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -930,7 +918,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -938,7 +926,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -946,7 +934,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -954,7 +942,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -962,7 +950,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -970,7 +958,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -978,7 +966,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1594,39 +1582,7 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>111</v>
-      </c>
-      <c r="B111" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-      <c r="B112" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-      <c r="B114" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/sku_mapping.xlsx
+++ b/sku_mapping.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="120">
   <si>
     <t>原始SKU</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>006-137-12G</t>
+  </si>
+  <si>
+    <t>008-137-12G</t>
   </si>
   <si>
     <t>WS007-30-TWIN</t>
@@ -702,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -718,7 +721,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -726,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -734,7 +737,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -742,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -750,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -758,7 +761,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -766,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -774,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -782,7 +785,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -790,7 +793,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -798,7 +801,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -806,7 +809,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -814,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -822,7 +825,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -830,7 +833,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -838,7 +841,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -846,7 +849,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -854,7 +857,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -862,7 +865,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -870,7 +873,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -878,7 +881,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -886,7 +889,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -894,7 +897,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -902,7 +905,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -910,7 +913,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -918,7 +921,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -926,7 +929,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -934,7 +937,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -942,7 +945,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -950,7 +953,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -958,7 +961,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -966,7 +969,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1583,6 +1586,14 @@
       </c>
       <c r="B110" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
